--- a/TestData/StockData.xlsx
+++ b/TestData/StockData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14730" windowHeight="5415" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14730" windowHeight="5415"/>
   </bookViews>
   <sheets>
     <sheet name="supplierdata" sheetId="1" r:id="rId1"/>
